--- a/docs/Data_Dictionary_v1.xlsx
+++ b/docs/Data_Dictionary_v1.xlsx
@@ -5,17 +5,17 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://shooliniuniversity-my.sharepoint.com/personal/ayushsharma1_shooliniuniversity_com/Documents/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ayush\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="209" documentId="8_{28D66C84-6EE5-40BF-AB47-AE52DF1710BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{95949C2B-92EC-415D-9854-2C513F4DC8D4}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15C48F33-6B62-42B3-B9AE-54B58EEA8695}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="6" activeTab="11" xr2:uid="{832DE8EA-1AF3-40B0-86F3-64BD0425EE00}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Customers" sheetId="1" r:id="rId1"/>
     <sheet name="Loan_Applications" sheetId="2" r:id="rId2"/>
-    <sheet name=" Credit_Assessment" sheetId="3" r:id="rId3"/>
+    <sheet name="Credit_Assessment" sheetId="3" r:id="rId3"/>
     <sheet name="Property" sheetId="4" r:id="rId4"/>
     <sheet name="Legal_Verification" sheetId="5" r:id="rId5"/>
     <sheet name="Technical_Valuation" sheetId="6" r:id="rId6"/>
@@ -26,31 +26,48 @@
     <sheet name="Rejection_Reasons" sheetId="11" r:id="rId11"/>
     <sheet name="Loan_Status_History" sheetId="12" r:id="rId12"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="2"/>
-    </ext>
-  </extLst>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="306" uniqueCount="147">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="615" uniqueCount="271">
+  <si>
+    <t>Table Name</t>
+  </si>
+  <si>
+    <t>Loan_Applications</t>
+  </si>
+  <si>
+    <t>Business Purpose</t>
+  </si>
+  <si>
+    <t>Stores information related to every loan application submitted by customers.</t>
+  </si>
+  <si>
+    <t>Primary Key</t>
+  </si>
+  <si>
+    <t>Loan_Application_ID</t>
+  </si>
+  <si>
+    <t>Owner</t>
+  </si>
+  <si>
+    <t>Credit Department</t>
+  </si>
+  <si>
+    <t>Source</t>
+  </si>
+  <si>
+    <t>Loan Application Form</t>
+  </si>
+  <si>
+    <t>Refresh Frequency</t>
+  </si>
+  <si>
+    <t>At Application / During Processing</t>
+  </si>
   <si>
     <t>Field Name</t>
   </si>
@@ -58,6 +75,426 @@
     <t>Business Name</t>
   </si>
   <si>
+    <t>Description</t>
+  </si>
+  <si>
+    <t>SQL Data Type</t>
+  </si>
+  <si>
+    <t>Excel Data Type</t>
+  </si>
+  <si>
+    <t>Allowed Values</t>
+  </si>
+  <si>
+    <t>Validation Rule</t>
+  </si>
+  <si>
+    <t>Foreign Key</t>
+  </si>
+  <si>
+    <t>Nullable</t>
+  </si>
+  <si>
+    <t>Derived Field</t>
+  </si>
+  <si>
+    <t>Example</t>
+  </si>
+  <si>
+    <t>Loan Application ID</t>
+  </si>
+  <si>
+    <t>Unique loan application identifier</t>
+  </si>
+  <si>
+    <t>VARCHAR(20)</t>
+  </si>
+  <si>
+    <t>Text</t>
+  </si>
+  <si>
+    <t>Starts with APP</t>
+  </si>
+  <si>
+    <t>Yes</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>APP000001</t>
+  </si>
+  <si>
+    <t>System</t>
+  </si>
+  <si>
+    <t>Customer_ID</t>
+  </si>
+  <si>
+    <t>Customer ID</t>
+  </si>
+  <si>
+    <t>Links to customer master</t>
+  </si>
+  <si>
+    <t>VARCHAR(15)</t>
+  </si>
+  <si>
+    <t>Must exist in Customers table</t>
+  </si>
+  <si>
+    <t>CUST000001</t>
+  </si>
+  <si>
+    <t>Customers</t>
+  </si>
+  <si>
+    <t>Loan_Purpose</t>
+  </si>
+  <si>
+    <t>Loan Purpose</t>
+  </si>
+  <si>
+    <t>Purpose of loan</t>
+  </si>
+  <si>
+    <t>VARCHAR(100)</t>
+  </si>
+  <si>
+    <t>Purchase, Construction, Renovation, Balance Transfer</t>
+  </si>
+  <si>
+    <t>Home Purchase</t>
+  </si>
+  <si>
+    <t>Application Form</t>
+  </si>
+  <si>
+    <t>Requested_Loan_Amount</t>
+  </si>
+  <si>
+    <t>Requested Loan Amount</t>
+  </si>
+  <si>
+    <t>Amount requested by customer</t>
+  </si>
+  <si>
+    <t>DECIMAL(18,2)</t>
+  </si>
+  <si>
+    <t>Number</t>
+  </si>
+  <si>
+    <t>Greater than 0</t>
+  </si>
+  <si>
+    <t>2500000</t>
+  </si>
+  <si>
+    <t>Application_Date</t>
+  </si>
+  <si>
+    <t>Application Date</t>
+  </si>
+  <si>
+    <t>Date application submitted</t>
+  </si>
+  <si>
+    <t>DATE</t>
+  </si>
+  <si>
+    <t>Date</t>
+  </si>
+  <si>
+    <t>Cannot be future date</t>
+  </si>
+  <si>
+    <t>2026-07-10</t>
+  </si>
+  <si>
+    <t>Application_Status</t>
+  </si>
+  <si>
+    <t>Application Status</t>
+  </si>
+  <si>
+    <t>Current application stage</t>
+  </si>
+  <si>
+    <t>VARCHAR(30)</t>
+  </si>
+  <si>
+    <t>Received, Under Review, Approved, Rejected, Disbursed</t>
+  </si>
+  <si>
+    <t>Under Review</t>
+  </si>
+  <si>
+    <t>Processing_Branch_ID</t>
+  </si>
+  <si>
+    <t>Processing Branch</t>
+  </si>
+  <si>
+    <t>Branch processing application</t>
+  </si>
+  <si>
+    <t>VARCHAR(10)</t>
+  </si>
+  <si>
+    <t>Must exist in Branches table</t>
+  </si>
+  <si>
+    <t>BR023</t>
+  </si>
+  <si>
+    <t>Branches</t>
+  </si>
+  <si>
+    <t>Assigned_Officer_ID</t>
+  </si>
+  <si>
+    <t>Assigned Officer</t>
+  </si>
+  <si>
+    <t>Credit officer assigned</t>
+  </si>
+  <si>
+    <t>Must exist in Employees table</t>
+  </si>
+  <si>
+    <t>EMP105</t>
+  </si>
+  <si>
+    <t>Employees</t>
+  </si>
+  <si>
+    <t>Processing_Remarks</t>
+  </si>
+  <si>
+    <t>Processing Remarks</t>
+  </si>
+  <si>
+    <t>Remarks related to loan processing.</t>
+  </si>
+  <si>
+    <t>VARCHAR(255)</t>
+  </si>
+  <si>
+    <t>Documents pending</t>
+  </si>
+  <si>
+    <t>Credit Officer</t>
+  </si>
+  <si>
+    <t>Loan_Product_ID</t>
+  </si>
+  <si>
+    <t>Loan Product</t>
+  </si>
+  <si>
+    <t>Unique identifier of the loan product selected by the customer</t>
+  </si>
+  <si>
+    <t>LP001, LP002, LP003, LP004</t>
+  </si>
+  <si>
+    <t>Must exist in Loan_Products table</t>
+  </si>
+  <si>
+    <t>LP001</t>
+  </si>
+  <si>
+    <t>Requested_Tenure_Months</t>
+  </si>
+  <si>
+    <t>Requested Tenure</t>
+  </si>
+  <si>
+    <t>Loan repayment period requested by the customer (months)</t>
+  </si>
+  <si>
+    <t>INT</t>
+  </si>
+  <si>
+    <t>12-360</t>
+  </si>
+  <si>
+    <t>240</t>
+  </si>
+  <si>
+    <t>Application_Channel</t>
+  </si>
+  <si>
+    <t>Application Channel</t>
+  </si>
+  <si>
+    <t>Channel through which the loan application was received</t>
+  </si>
+  <si>
+    <t>Branch, Online, RM, Referral</t>
+  </si>
+  <si>
+    <t>Must be from predefined list</t>
+  </si>
+  <si>
+    <t>Branch</t>
+  </si>
+  <si>
+    <t>Branch that received and processed the loan application</t>
+  </si>
+  <si>
+    <t>BR001-BR999</t>
+  </si>
+  <si>
+    <t>Branch Master</t>
+  </si>
+  <si>
+    <t>Current_Stage</t>
+  </si>
+  <si>
+    <t>Current Processing Stage</t>
+  </si>
+  <si>
+    <t>Current stage of the loan processing workflow</t>
+  </si>
+  <si>
+    <t>VARCHAR(50)</t>
+  </si>
+  <si>
+    <t>Application Received, Documents Pending, CIBIL Verification, Income Verification, Eligibility Calculation, Legal Verification, Technical Valuation, Credit Assessment, Approved, Rejected, Disbursed</t>
+  </si>
+  <si>
+    <t>Income Verification</t>
+  </si>
+  <si>
+    <t>System Generated</t>
+  </si>
+  <si>
+    <t>Received_Date</t>
+  </si>
+  <si>
+    <t>Received Date</t>
+  </si>
+  <si>
+    <t>Date on which the bank officialy received the application</t>
+  </si>
+  <si>
+    <t>Valid Date</t>
+  </si>
+  <si>
+    <t>Documents_Completed_Date</t>
+  </si>
+  <si>
+    <t>Documents Completed Date</t>
+  </si>
+  <si>
+    <t>Date on which all required documents were received and verified for further processing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Must be on or after Received Date </t>
+  </si>
+  <si>
+    <t>Loan Processing Form</t>
+  </si>
+  <si>
+    <t>Credit_Decision_Date</t>
+  </si>
+  <si>
+    <t>Credit Decision Date</t>
+  </si>
+  <si>
+    <t>Date on which the Credit Officer or Credit Manager made the final credit decision on the loan application</t>
+  </si>
+  <si>
+    <t>Must be on or after Documents_Completed_Date</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Credit Department </t>
+  </si>
+  <si>
+    <t>Disbursement_Date</t>
+  </si>
+  <si>
+    <t>Disbursement Date</t>
+  </si>
+  <si>
+    <t>Date on which the approved loan amount was disbursed to the customer.</t>
+  </si>
+  <si>
+    <t>Must be on or after Credit_Decision_Date</t>
+  </si>
+  <si>
+    <t>Loan Disbursement System</t>
+  </si>
+  <si>
+    <t>Processing_Unit</t>
+  </si>
+  <si>
+    <t>Processing Unit</t>
+  </si>
+  <si>
+    <t>Unit responsible for processing the application based on routing rules (e.g., Branch or Regional Credit Unit).</t>
+  </si>
+  <si>
+    <t>Branch, Regional Credit Unit</t>
+  </si>
+  <si>
+    <t>System Routing</t>
+  </si>
+  <si>
+    <t>Assigned_Date</t>
+  </si>
+  <si>
+    <t>Assigned Date</t>
+  </si>
+  <si>
+    <t>Date on which the application was assigned to a processing officer.</t>
+  </si>
+  <si>
+    <t>Must be on or after Received_Date</t>
+  </si>
+  <si>
+    <t>2026-07-11</t>
+  </si>
+  <si>
+    <t>Workflow System</t>
+  </si>
+  <si>
+    <t>Assigned_By_Employee_ID</t>
+  </si>
+  <si>
+    <t>Assigned By Employee</t>
+  </si>
+  <si>
+    <t>Employee ID of the manager who assigned the application.</t>
+  </si>
+  <si>
+    <t>EMP001</t>
+  </si>
+  <si>
+    <t>Employee ID of the credit officer assigned to process the application.</t>
+  </si>
+  <si>
+    <t>Routing_Reason</t>
+  </si>
+  <si>
+    <t>Routing Reason</t>
+  </si>
+  <si>
+    <t>Reason why the application was routed to the selected processing unit.</t>
+  </si>
+  <si>
+    <t>Branch Threshold, Regional Credit Unit Threshold</t>
+  </si>
+  <si>
+    <t>Must match routing policy</t>
+  </si>
+  <si>
+    <t>Regional Credit Unit Threshold</t>
+  </si>
+  <si>
     <t xml:space="preserve">Description </t>
   </si>
   <si>
@@ -67,57 +504,15 @@
     <t xml:space="preserve">Excel Data Type </t>
   </si>
   <si>
-    <t>Allowed Values</t>
-  </si>
-  <si>
-    <t>Validation Rule</t>
-  </si>
-  <si>
-    <t>Primary Key</t>
-  </si>
-  <si>
-    <t>Foreign Key</t>
-  </si>
-  <si>
-    <t>Nullable</t>
-  </si>
-  <si>
-    <t>Derived Field</t>
-  </si>
-  <si>
     <t xml:space="preserve">Example </t>
   </si>
   <si>
-    <t>Source</t>
-  </si>
-  <si>
-    <t>Customer_ID</t>
-  </si>
-  <si>
-    <t>Customer ID</t>
-  </si>
-  <si>
     <t>Unique customer identifier</t>
   </si>
   <si>
-    <t>VARCHAR(15)</t>
-  </si>
-  <si>
-    <t>Text</t>
-  </si>
-  <si>
     <t>Unique, starts with CUST</t>
   </si>
   <si>
-    <t>Yes</t>
-  </si>
-  <si>
-    <t>No</t>
-  </si>
-  <si>
-    <t>CUST000001</t>
-  </si>
-  <si>
     <t>Project</t>
   </si>
   <si>
@@ -130,9 +525,6 @@
     <t>Customer first name</t>
   </si>
   <si>
-    <t>VARCHAR(50)</t>
-  </si>
-  <si>
     <t>Alphabetic</t>
   </si>
   <si>
@@ -160,9 +552,6 @@
     <t>Customer gender</t>
   </si>
   <si>
-    <t>VARCHAR(10)</t>
-  </si>
-  <si>
     <t>Male/Female/Other</t>
   </si>
   <si>
@@ -178,12 +567,6 @@
     <t>Birth date</t>
   </si>
   <si>
-    <t>DATE</t>
-  </si>
-  <si>
-    <t>Date</t>
-  </si>
-  <si>
     <t>Valid date</t>
   </si>
   <si>
@@ -196,12 +579,6 @@
     <t>Calculated from DOB</t>
   </si>
   <si>
-    <t>INT</t>
-  </si>
-  <si>
-    <t>Number</t>
-  </si>
-  <si>
     <t>18-70</t>
   </si>
   <si>
@@ -220,9 +597,6 @@
     <t>Marital status</t>
   </si>
   <si>
-    <t>VARCHAR(20)</t>
-  </si>
-  <si>
     <t>Single/Married/Other</t>
   </si>
   <si>
@@ -247,64 +621,7 @@
     <t>Employment Type</t>
   </si>
   <si>
-    <t>Salaried</t>
-  </si>
-  <si>
-    <t>Internship Observation</t>
-  </si>
-  <si>
-    <t>Annual_Income</t>
-  </si>
-  <si>
-    <t>Annual Income</t>
-  </si>
-  <si>
-    <t>DECIMAL</t>
-  </si>
-  <si>
-    <t>Positive</t>
-  </si>
-  <si>
-    <t>840000</t>
-  </si>
-  <si>
-    <t>Verified</t>
-  </si>
-  <si>
-    <t>Net_Monthly_Income</t>
-  </si>
-  <si>
-    <t>Net Monthly Income</t>
-  </si>
-  <si>
-    <t>Net income used for eligibility</t>
-  </si>
-  <si>
-    <t>70000</t>
-  </si>
-  <si>
-    <t>City</t>
-  </si>
-  <si>
-    <t>Customer city</t>
-  </si>
-  <si>
-    <t>Chandigarh</t>
-  </si>
-  <si>
-    <t>District</t>
-  </si>
-  <si>
-    <t>Customer district</t>
-  </si>
-  <si>
-    <t>State</t>
-  </si>
-  <si>
-    <t>Customer state</t>
-  </si>
-  <si>
-    <t>Punjab</t>
+    <t>Indicates how the customer earns income.</t>
   </si>
   <si>
     <t>Salaried
@@ -314,12 +631,78 @@
 Pensioner</t>
   </si>
   <si>
+    <t>Salaried</t>
+  </si>
+  <si>
+    <t>Internship Observation</t>
+  </si>
+  <si>
+    <t>Annual_Income</t>
+  </si>
+  <si>
+    <t>Annual Income</t>
+  </si>
+  <si>
     <t>Verified Annual Gross Income</t>
   </si>
   <si>
+    <t>DECIMAL</t>
+  </si>
+  <si>
+    <t>Positive</t>
+  </si>
+  <si>
+    <t>840000</t>
+  </si>
+  <si>
+    <t>Verified</t>
+  </si>
+  <si>
+    <t>Net_Monthly_Income</t>
+  </si>
+  <si>
+    <t>Net Monthly Income</t>
+  </si>
+  <si>
+    <t>Net income used for eligibility</t>
+  </si>
+  <si>
+    <t>70000</t>
+  </si>
+  <si>
+    <t>City</t>
+  </si>
+  <si>
+    <t>Customer city</t>
+  </si>
+  <si>
+    <t>Chandigarh</t>
+  </si>
+  <si>
+    <t>District</t>
+  </si>
+  <si>
+    <t>Customer district</t>
+  </si>
+  <si>
+    <t>State</t>
+  </si>
+  <si>
+    <t>Customer state</t>
+  </si>
+  <si>
+    <t>Punjab</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Customer_Type </t>
+  </si>
+  <si>
     <t>Customer Type</t>
   </si>
   <si>
+    <t>Indicates whether the applicant is a new or existing customer of the bank</t>
+  </si>
+  <si>
     <t>New/Existing</t>
   </si>
   <si>
@@ -341,9 +724,6 @@
     <t>Government Employee, Private Employee, Doctor, CA, Advocate, Shopkeeper, Farmer, Business Owner, Engineer, Teacher, etc.</t>
   </si>
   <si>
-    <t>Must be from predefined list</t>
-  </si>
-  <si>
     <t>Government Teacher</t>
   </si>
   <si>
@@ -353,20 +733,10 @@
     <t>Pan Verification Status</t>
   </si>
   <si>
-    <r>
-      <t xml:space="preserve">BOOLEAN </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>(or VARCHAR(3) if using Yes/No)</t>
-    </r>
+    <t>Indicates whether the applicant's PAN has been verified</t>
+  </si>
+  <si>
+    <t>BOOLEAN (or VARCHAR(3) if using Yes/No)</t>
   </si>
   <si>
     <t>Yes/No</t>
@@ -384,9 +754,18 @@
     <t>Aadhaar Verification Status</t>
   </si>
   <si>
+    <t>Indicates whether the applicant's Aadhaar has been verified</t>
+  </si>
+  <si>
     <t>Mobile_Number</t>
   </si>
   <si>
+    <t>Mobile Number</t>
+  </si>
+  <si>
+    <t>Customer Mobile Number (Synthetic)</t>
+  </si>
+  <si>
     <t>10-digit number</t>
   </si>
   <si>
@@ -402,15 +781,12 @@
     <t>Customer email (syntheic)</t>
   </si>
   <si>
-    <t>VARCHAR(100)</t>
+    <t>Valid email format</t>
   </si>
   <si>
     <t>Must contain @</t>
   </si>
   <si>
-    <t>Valid email format</t>
-  </si>
-  <si>
     <t>cust0001@example.com</t>
   </si>
   <si>
@@ -420,19 +796,49 @@
     <t xml:space="preserve">Home Branch </t>
   </si>
   <si>
-    <t>BR023</t>
-  </si>
-  <si>
-    <t>Application_Date</t>
+    <t>Branch where customer applied for loan</t>
+  </si>
+  <si>
+    <t>BR001-BR150</t>
+  </si>
+  <si>
+    <t>Date on which the customer submitted the application form</t>
+  </si>
+  <si>
+    <t>date</t>
+  </si>
+  <si>
+    <t>Cannot be a future date</t>
   </si>
   <si>
     <t>Customer_Status</t>
   </si>
   <si>
+    <t>Customer status</t>
+  </si>
+  <si>
+    <t>Current relationship status with bank</t>
+  </si>
+  <si>
+    <t>Active, Inactive, Closed</t>
+  </si>
+  <si>
+    <t>Must be one of the allowed values</t>
+  </si>
+  <si>
     <t>Active</t>
   </si>
   <si>
+    <t>Customer Master</t>
+  </si>
+  <si>
     <t>Risk_Category</t>
+  </si>
+  <si>
+    <t>Risk Category</t>
+  </si>
+  <si>
+    <t>Overall customer risk category</t>
   </si>
   <si>
     <t>Low
@@ -440,84 +846,19 @@
 High</t>
   </si>
   <si>
-    <t xml:space="preserve">Customer_Type </t>
-  </si>
-  <si>
-    <t>Indicates how the customer earns income.</t>
-  </si>
-  <si>
-    <t>Branch where customer applied for loan</t>
-  </si>
-  <si>
-    <t>BR001-BR150</t>
-  </si>
-  <si>
-    <t>Application Date</t>
-  </si>
-  <si>
-    <t>Date on which the customer submitted the application form</t>
-  </si>
-  <si>
-    <t>Cannot be a future date</t>
-  </si>
-  <si>
-    <t>date</t>
-  </si>
-  <si>
-    <t>Customer status</t>
-  </si>
-  <si>
-    <t>Current relationship status with bank</t>
-  </si>
-  <si>
-    <t>Active, Inactive, Closed</t>
-  </si>
-  <si>
-    <t>Must be one of the allowed values</t>
-  </si>
-  <si>
-    <t>Customer Master</t>
-  </si>
-  <si>
-    <t>Risk Category</t>
-  </si>
-  <si>
-    <t>Overall customer risk category</t>
-  </si>
-  <si>
     <t>Calculated from credit assessment</t>
   </si>
   <si>
     <t>Medium</t>
-  </si>
-  <si>
-    <t>Indicates whether the applicant is a new or existing customer of the bank</t>
-  </si>
-  <si>
-    <t>Indicates whether the applicant's PAN has been verified</t>
-  </si>
-  <si>
-    <t>Indicates whether the applicant's Aadhaar has been verified</t>
-  </si>
-  <si>
-    <t>Loan Application Form</t>
-  </si>
-  <si>
-    <t>Mobile Number</t>
-  </si>
-  <si>
-    <t>Customer Mobile Number (Synthetic)</t>
-  </si>
-  <si>
-    <t>Must exist in Branches table</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy/mm/dd"/>
+    <numFmt numFmtId="165" formatCode="yyyy\-mm\-dd\ h:mm:ss"/>
   </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
@@ -536,12 +877,9 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
+      <b/>
       <sz val="11"/>
-      <color theme="1"/>
       <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -564,7 +902,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -576,6 +914,15 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -592,10 +939,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -914,997 +1257,997 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{42E664B1-D6D4-4BC9-B611-CC2B90989978}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:M26"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="17.88671875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="23" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="59.21875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="35.88671875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.33203125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="104.33203125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="23.44140625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.88671875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="10.44140625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="8.109375" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="12" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="18" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="22.5546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="18.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="23.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="61.5546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="36.6640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="105.88671875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="24.77734375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.33203125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="11.109375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="8.44140625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="12.44140625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="18.109375" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="23.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>2</v>
+        <v>154</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>3</v>
+        <v>155</v>
       </c>
       <c r="E1" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="H1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>7</v>
-      </c>
       <c r="I1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="M1" s="1" t="s">
         <v>8</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="B2" t="s">
-        <v>14</v>
+        <v>33</v>
       </c>
       <c r="C2" t="s">
-        <v>15</v>
+        <v>158</v>
       </c>
       <c r="D2" t="s">
-        <v>16</v>
+        <v>35</v>
       </c>
       <c r="E2" t="s">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="G2" t="s">
-        <v>18</v>
+        <v>159</v>
       </c>
       <c r="H2" t="s">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="I2" t="s">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="J2" t="s">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="K2" t="s">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="L2" t="s">
-        <v>21</v>
+        <v>37</v>
       </c>
       <c r="M2" t="s">
-        <v>22</v>
+        <v>160</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>23</v>
+        <v>161</v>
       </c>
       <c r="B3" t="s">
-        <v>24</v>
+        <v>162</v>
       </c>
       <c r="C3" t="s">
-        <v>25</v>
+        <v>163</v>
       </c>
       <c r="D3" t="s">
+        <v>109</v>
+      </c>
+      <c r="E3" t="s">
         <v>26</v>
       </c>
-      <c r="E3" t="s">
-        <v>17</v>
-      </c>
       <c r="G3" t="s">
-        <v>27</v>
+        <v>164</v>
       </c>
       <c r="H3" t="s">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="I3" t="s">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="J3" t="s">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="K3" t="s">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="L3" t="s">
-        <v>28</v>
+        <v>165</v>
       </c>
       <c r="M3" t="s">
-        <v>29</v>
+        <v>166</v>
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>30</v>
+        <v>167</v>
       </c>
       <c r="B4" t="s">
-        <v>31</v>
+        <v>168</v>
       </c>
       <c r="C4" t="s">
-        <v>32</v>
+        <v>169</v>
       </c>
       <c r="D4" t="s">
+        <v>109</v>
+      </c>
+      <c r="E4" t="s">
         <v>26</v>
       </c>
-      <c r="E4" t="s">
-        <v>17</v>
-      </c>
       <c r="G4" t="s">
-        <v>27</v>
+        <v>164</v>
       </c>
       <c r="H4" t="s">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="I4" t="s">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="J4" t="s">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="K4" t="s">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="L4" t="s">
-        <v>33</v>
+        <v>170</v>
       </c>
       <c r="M4" t="s">
-        <v>29</v>
+        <v>166</v>
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>34</v>
+        <v>171</v>
       </c>
       <c r="B5" t="s">
-        <v>34</v>
+        <v>171</v>
       </c>
       <c r="C5" t="s">
-        <v>35</v>
+        <v>172</v>
       </c>
       <c r="D5" t="s">
-        <v>36</v>
+        <v>69</v>
       </c>
       <c r="E5" t="s">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="F5" t="s">
-        <v>37</v>
+        <v>173</v>
       </c>
       <c r="H5" t="s">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="I5" t="s">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="J5" t="s">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="K5" t="s">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="L5" t="s">
-        <v>38</v>
+        <v>174</v>
       </c>
       <c r="M5" t="s">
-        <v>29</v>
+        <v>166</v>
       </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>39</v>
+        <v>175</v>
       </c>
       <c r="B6" t="s">
-        <v>40</v>
+        <v>176</v>
       </c>
       <c r="C6" t="s">
-        <v>41</v>
+        <v>177</v>
       </c>
       <c r="D6" t="s">
-        <v>42</v>
+        <v>56</v>
       </c>
       <c r="E6" t="s">
-        <v>43</v>
+        <v>57</v>
       </c>
       <c r="G6" t="s">
-        <v>44</v>
+        <v>178</v>
       </c>
       <c r="H6" t="s">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="I6" t="s">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="J6" t="s">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="K6" t="s">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="L6" t="s">
-        <v>45</v>
+        <v>179</v>
       </c>
       <c r="M6" t="s">
-        <v>29</v>
+        <v>166</v>
       </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>46</v>
+        <v>180</v>
       </c>
       <c r="B7" t="s">
-        <v>46</v>
+        <v>180</v>
       </c>
       <c r="C7" t="s">
-        <v>47</v>
+        <v>181</v>
       </c>
       <c r="D7" t="s">
-        <v>48</v>
+        <v>94</v>
       </c>
       <c r="E7" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G7" t="s">
-        <v>50</v>
+        <v>182</v>
       </c>
       <c r="H7" t="s">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="I7" t="s">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="J7" t="s">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="K7" t="s">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="L7" t="s">
-        <v>51</v>
+        <v>183</v>
       </c>
       <c r="M7" t="s">
-        <v>52</v>
+        <v>184</v>
       </c>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>53</v>
+        <v>185</v>
       </c>
       <c r="B8" t="s">
-        <v>54</v>
+        <v>186</v>
       </c>
       <c r="C8" t="s">
-        <v>55</v>
+        <v>187</v>
       </c>
       <c r="D8" t="s">
-        <v>56</v>
+        <v>25</v>
       </c>
       <c r="E8" t="s">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="F8" t="s">
-        <v>57</v>
+        <v>188</v>
       </c>
       <c r="H8" t="s">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="I8" t="s">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="J8" t="s">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="K8" t="s">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="L8" t="s">
-        <v>58</v>
+        <v>189</v>
       </c>
       <c r="M8" t="s">
-        <v>29</v>
+        <v>166</v>
       </c>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>59</v>
+        <v>190</v>
       </c>
       <c r="B9" t="s">
-        <v>59</v>
+        <v>190</v>
       </c>
       <c r="C9" t="s">
-        <v>60</v>
+        <v>191</v>
       </c>
       <c r="D9" t="s">
-        <v>48</v>
+        <v>94</v>
       </c>
       <c r="E9" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G9" t="s">
-        <v>61</v>
+        <v>192</v>
       </c>
       <c r="H9" t="s">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="I9" t="s">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="J9" t="s">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="K9" t="s">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="L9" t="s">
-        <v>62</v>
+        <v>193</v>
       </c>
       <c r="M9" t="s">
-        <v>29</v>
+        <v>166</v>
       </c>
     </row>
     <row r="10" spans="1:13" ht="72" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>63</v>
+        <v>194</v>
       </c>
       <c r="B10" t="s">
-        <v>64</v>
+        <v>195</v>
       </c>
       <c r="C10" t="s">
-        <v>124</v>
+        <v>196</v>
       </c>
       <c r="D10" t="s">
-        <v>56</v>
+        <v>25</v>
       </c>
       <c r="E10" t="s">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>85</v>
+        <v>197</v>
       </c>
       <c r="H10" t="s">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="I10" t="s">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="J10" t="s">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="K10" t="s">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="L10" t="s">
-        <v>65</v>
+        <v>198</v>
       </c>
       <c r="M10" t="s">
-        <v>66</v>
+        <v>199</v>
       </c>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>67</v>
+        <v>200</v>
       </c>
       <c r="B11" t="s">
-        <v>68</v>
+        <v>201</v>
       </c>
       <c r="C11" t="s">
-        <v>86</v>
+        <v>202</v>
       </c>
       <c r="D11" t="s">
-        <v>69</v>
+        <v>203</v>
       </c>
       <c r="E11" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G11" t="s">
-        <v>70</v>
+        <v>204</v>
       </c>
       <c r="H11" t="s">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="I11" t="s">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="J11" t="s">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="K11" t="s">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="L11" t="s">
-        <v>71</v>
+        <v>205</v>
       </c>
       <c r="M11" t="s">
-        <v>72</v>
+        <v>206</v>
       </c>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>73</v>
+        <v>207</v>
       </c>
       <c r="B12" t="s">
-        <v>74</v>
+        <v>208</v>
       </c>
       <c r="C12" t="s">
-        <v>75</v>
+        <v>209</v>
       </c>
       <c r="D12" t="s">
-        <v>69</v>
+        <v>203</v>
       </c>
       <c r="E12" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G12" t="s">
-        <v>70</v>
+        <v>204</v>
       </c>
       <c r="H12" t="s">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="I12" t="s">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="J12" t="s">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="K12" t="s">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="L12" t="s">
-        <v>76</v>
+        <v>210</v>
       </c>
       <c r="M12" t="s">
-        <v>72</v>
+        <v>206</v>
       </c>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>77</v>
+        <v>211</v>
       </c>
       <c r="B13" t="s">
-        <v>77</v>
+        <v>211</v>
       </c>
       <c r="C13" t="s">
-        <v>78</v>
+        <v>212</v>
       </c>
       <c r="D13" t="s">
+        <v>109</v>
+      </c>
+      <c r="E13" t="s">
         <v>26</v>
       </c>
-      <c r="E13" t="s">
-        <v>17</v>
-      </c>
       <c r="H13" t="s">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="I13" t="s">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="J13" t="s">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="K13" t="s">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="L13" t="s">
-        <v>79</v>
+        <v>213</v>
       </c>
       <c r="M13" t="s">
-        <v>29</v>
+        <v>166</v>
       </c>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>80</v>
+        <v>214</v>
       </c>
       <c r="B14" t="s">
-        <v>80</v>
+        <v>214</v>
       </c>
       <c r="C14" t="s">
-        <v>81</v>
+        <v>215</v>
       </c>
       <c r="D14" t="s">
+        <v>109</v>
+      </c>
+      <c r="E14" t="s">
         <v>26</v>
       </c>
-      <c r="E14" t="s">
-        <v>17</v>
-      </c>
       <c r="H14" t="s">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="I14" t="s">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="J14" t="s">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="K14" t="s">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="L14" t="s">
-        <v>79</v>
+        <v>213</v>
       </c>
       <c r="M14" t="s">
-        <v>29</v>
+        <v>166</v>
       </c>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>82</v>
+        <v>216</v>
       </c>
       <c r="B15" t="s">
-        <v>82</v>
+        <v>216</v>
       </c>
       <c r="C15" t="s">
-        <v>83</v>
+        <v>217</v>
       </c>
       <c r="D15" t="s">
+        <v>109</v>
+      </c>
+      <c r="E15" t="s">
         <v>26</v>
       </c>
-      <c r="E15" t="s">
-        <v>17</v>
-      </c>
       <c r="H15" t="s">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="I15" t="s">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="J15" t="s">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="K15" t="s">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="L15" t="s">
-        <v>84</v>
+        <v>218</v>
       </c>
       <c r="M15" t="s">
-        <v>29</v>
+        <v>166</v>
       </c>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>123</v>
+        <v>219</v>
       </c>
       <c r="B16" t="s">
-        <v>87</v>
+        <v>220</v>
       </c>
       <c r="C16" t="s">
-        <v>140</v>
+        <v>221</v>
       </c>
       <c r="D16" t="s">
-        <v>56</v>
+        <v>25</v>
       </c>
       <c r="E16" t="s">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="F16" t="s">
-        <v>88</v>
+        <v>222</v>
       </c>
       <c r="G16" t="s">
-        <v>89</v>
+        <v>223</v>
       </c>
       <c r="H16" t="s">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="I16" t="s">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="J16" t="s">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="K16" t="s">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="L16" t="s">
-        <v>90</v>
+        <v>224</v>
       </c>
       <c r="M16" t="s">
-        <v>91</v>
+        <v>225</v>
       </c>
     </row>
     <row r="17" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>92</v>
+        <v>226</v>
       </c>
       <c r="B17" t="s">
-        <v>92</v>
+        <v>226</v>
       </c>
       <c r="C17" t="s">
-        <v>93</v>
+        <v>227</v>
       </c>
       <c r="D17" t="s">
+        <v>109</v>
+      </c>
+      <c r="E17" t="s">
         <v>26</v>
       </c>
-      <c r="E17" t="s">
-        <v>17</v>
-      </c>
       <c r="F17" t="s">
-        <v>94</v>
+        <v>228</v>
       </c>
       <c r="G17" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="H17" t="s">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="I17" t="s">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="J17" t="s">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="K17" t="s">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="L17" t="s">
-        <v>96</v>
+        <v>229</v>
       </c>
       <c r="M17" t="s">
-        <v>91</v>
+        <v>225</v>
       </c>
     </row>
     <row r="18" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>97</v>
+        <v>230</v>
       </c>
       <c r="B18" t="s">
-        <v>98</v>
+        <v>231</v>
       </c>
       <c r="C18" t="s">
-        <v>141</v>
+        <v>232</v>
       </c>
       <c r="D18" t="s">
-        <v>99</v>
+        <v>233</v>
       </c>
       <c r="E18" t="s">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="F18" t="s">
-        <v>100</v>
+        <v>234</v>
       </c>
       <c r="G18" t="s">
-        <v>101</v>
+        <v>235</v>
       </c>
       <c r="H18" t="s">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="I18" t="s">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="J18" t="s">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="K18" t="s">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="L18" t="s">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="M18" t="s">
-        <v>102</v>
+        <v>236</v>
       </c>
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>103</v>
+        <v>237</v>
       </c>
       <c r="B19" t="s">
-        <v>104</v>
+        <v>238</v>
       </c>
       <c r="C19" t="s">
-        <v>142</v>
+        <v>239</v>
       </c>
       <c r="D19" t="s">
-        <v>99</v>
+        <v>233</v>
       </c>
       <c r="E19" t="s">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="F19" t="s">
-        <v>100</v>
+        <v>234</v>
       </c>
       <c r="G19" t="s">
-        <v>101</v>
+        <v>235</v>
       </c>
       <c r="H19" t="s">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="I19" t="s">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="J19" t="s">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="K19" t="s">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="L19" t="s">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="M19" t="s">
-        <v>102</v>
+        <v>236</v>
       </c>
     </row>
     <row r="20" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>105</v>
+        <v>240</v>
       </c>
       <c r="B20" t="s">
-        <v>144</v>
+        <v>241</v>
       </c>
       <c r="C20" t="s">
-        <v>145</v>
+        <v>242</v>
       </c>
       <c r="D20" t="s">
-        <v>36</v>
+        <v>69</v>
       </c>
       <c r="E20" t="s">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="F20" t="s">
-        <v>106</v>
+        <v>243</v>
       </c>
       <c r="G20" t="s">
-        <v>107</v>
+        <v>244</v>
       </c>
       <c r="H20" t="s">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="I20" t="s">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="J20" t="s">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="K20" t="s">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="L20">
         <v>9876543210</v>
       </c>
       <c r="M20" t="s">
-        <v>29</v>
+        <v>166</v>
       </c>
     </row>
     <row r="21" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>108</v>
+        <v>245</v>
       </c>
       <c r="B21" t="s">
-        <v>109</v>
+        <v>246</v>
       </c>
       <c r="C21" t="s">
-        <v>110</v>
+        <v>247</v>
       </c>
       <c r="D21" t="s">
-        <v>111</v>
+        <v>42</v>
       </c>
       <c r="E21" t="s">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="F21" t="s">
-        <v>113</v>
+        <v>248</v>
       </c>
       <c r="G21" t="s">
-        <v>112</v>
+        <v>249</v>
       </c>
       <c r="H21" t="s">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="I21" t="s">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="J21" t="s">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="K21" t="s">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="L21" s="3" t="s">
-        <v>114</v>
+        <v>250</v>
       </c>
       <c r="M21" t="s">
-        <v>29</v>
+        <v>166</v>
       </c>
     </row>
     <row r="22" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>115</v>
+        <v>251</v>
       </c>
       <c r="B22" t="s">
-        <v>116</v>
+        <v>252</v>
       </c>
       <c r="C22" t="s">
-        <v>125</v>
+        <v>253</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>36</v>
+        <v>69</v>
       </c>
       <c r="E22" t="s">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="F22" t="s">
-        <v>126</v>
+        <v>254</v>
       </c>
       <c r="G22" t="s">
-        <v>146</v>
+        <v>70</v>
       </c>
       <c r="H22" t="s">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="I22" t="s">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="J22" t="s">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="K22" t="s">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="L22" t="s">
-        <v>117</v>
+        <v>71</v>
       </c>
       <c r="M22" t="s">
-        <v>91</v>
+        <v>225</v>
       </c>
     </row>
     <row r="23" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>118</v>
+        <v>53</v>
       </c>
       <c r="B23" t="s">
-        <v>127</v>
+        <v>54</v>
       </c>
       <c r="C23" t="s">
-        <v>128</v>
+        <v>255</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>43</v>
+        <v>57</v>
       </c>
       <c r="E23" t="s">
-        <v>130</v>
+        <v>256</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>44</v>
+        <v>178</v>
       </c>
       <c r="G23" t="s">
-        <v>129</v>
+        <v>257</v>
       </c>
       <c r="H23" t="s">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="I23" t="s">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="J23" t="s">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="K23" t="s">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="L23" s="4">
         <v>46213</v>
       </c>
       <c r="M23" t="s">
-        <v>143</v>
+        <v>9</v>
       </c>
     </row>
     <row r="24" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>119</v>
+        <v>258</v>
       </c>
       <c r="B24" t="s">
-        <v>131</v>
+        <v>259</v>
       </c>
       <c r="C24" t="s">
-        <v>132</v>
+        <v>260</v>
       </c>
       <c r="D24" t="s">
-        <v>56</v>
+        <v>25</v>
       </c>
       <c r="E24" t="s">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>133</v>
+        <v>261</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>134</v>
+        <v>262</v>
       </c>
       <c r="H24" t="s">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="I24" t="s">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="J24" t="s">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="K24" t="s">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="L24" t="s">
-        <v>120</v>
+        <v>263</v>
       </c>
       <c r="M24" t="s">
-        <v>135</v>
+        <v>264</v>
       </c>
     </row>
     <row r="25" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>121</v>
+        <v>265</v>
       </c>
       <c r="B25" t="s">
-        <v>136</v>
+        <v>266</v>
       </c>
       <c r="C25" t="s">
-        <v>137</v>
+        <v>267</v>
       </c>
       <c r="D25" t="s">
-        <v>56</v>
+        <v>25</v>
       </c>
       <c r="E25" t="s">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>122</v>
+        <v>268</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>138</v>
+        <v>269</v>
       </c>
       <c r="H25" t="s">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="I25" t="s">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="J25" t="s">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="K25" t="s">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="L25" t="s">
-        <v>139</v>
+        <v>270</v>
       </c>
       <c r="M25" t="s">
-        <v>52</v>
+        <v>184</v>
       </c>
     </row>
     <row r="26" spans="1:13" x14ac:dyDescent="0.3">
@@ -1916,7 +2259,7 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A9EE9BB6-AD0D-4537-B51A-DA49148D1F65}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData/>
@@ -1925,7 +2268,7 @@
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0AA42348-1984-4FA2-AC76-94BEE8023EA5}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData/>
@@ -1934,7 +2277,7 @@
 </file>
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4C565B8F-D286-4DCE-B959-DE496EDA777C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData/>
@@ -1943,16 +2286,1036 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8F986EB6-A515-476E-804C-7ECA90A7EA50}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <sheetData/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1:N32"/>
+  <sheetFormatPr defaultColWidth="42.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="24.6640625" style="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="23.77734375" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="49.109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.33203125" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="46.5546875" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="40.109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="24.33203125" style="2" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10.44140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="8.109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="12" style="2" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="17" style="2" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="22.88671875" style="2" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.77734375" style="2" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="42.5546875" style="2" customWidth="1"/>
+    <col min="16" max="16384" width="42.5546875" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A1" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A2" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A3" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A4" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A5" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A6" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A8" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="D8" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="E8" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="F8" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="G8" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="H8" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="I8" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="J8" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="K8" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="L8" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="M8" s="6" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A9" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="I9" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="J9" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="K9" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="L9" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="M9" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A10" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="I10" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="J10" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="K10" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="L10" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="M10" s="2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A11" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="I11" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="J11" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="K11" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="L11" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="M11" s="2" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A12" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="G12" t="s">
+        <v>51</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="I12" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="J12" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="K12" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="L12" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="M12" s="2" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A13" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="I13" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="J13" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="K13" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="L13" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="M13" s="2" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A14" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="F14" t="s">
+        <v>64</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="I14" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="J14" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="K14" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="L14" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="M14" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A15" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="G15" t="s">
+        <v>70</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="I15" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="J15" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="K15" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="L15" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="M15" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A16" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="I16" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="J16" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="K16" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="L16" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="M16" s="2" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A17" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="I17" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="J17" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="K17" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="L17" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="M17" s="2" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A18" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="F18" t="s">
+        <v>88</v>
+      </c>
+      <c r="G18" t="s">
+        <v>89</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="I18" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="J18" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="K18" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="L18" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="M18" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A19" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="G19" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="I19" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="J19" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="K19" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="L19" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="M19" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="20" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A20" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="F20" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="I20" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="J20" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="K20" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="L20" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="M20" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A21" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="F21" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="G21" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="H21" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="I21" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="J21" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="K21" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="L21" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="M21" s="2" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="22" spans="1:14" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A22" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="F22" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="G22" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="H22" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="I22" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="J22" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="K22" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="L22" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="M22" s="2" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="23" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A23" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="F23" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="G23" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="H23" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="I23" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="J23" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="K23" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="L23" s="8">
+        <v>46213</v>
+      </c>
+      <c r="M23" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="24" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A24" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="F24" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="G24" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="H24" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="I24" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="J24" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="K24" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="L24" s="8">
+        <v>46215</v>
+      </c>
+      <c r="M24" s="2" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="25" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A25" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="F25" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="G25" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="H25" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="I25" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="J25" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="K25" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="L25" s="7">
+        <v>46218</v>
+      </c>
+      <c r="M25" s="2" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="26" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A26" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="F26" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="G26" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="H26" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="I26" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="J26" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="K26" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="L26" s="7">
+        <v>46221</v>
+      </c>
+      <c r="M26" s="2" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="27" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A27" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="F27" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="G27" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="H27" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="I27" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="J27" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="K27" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="L27" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="M27" s="2" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="28" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A28" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="F28" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="G28" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="H28" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="I28" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="J28" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="K28" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="L28" s="7" t="s">
+        <v>141</v>
+      </c>
+      <c r="M28" s="2" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="29" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A29" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="C29" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="G29" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="H29" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="I29" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="J29" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="K29" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="L29" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="M29" s="2" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="30" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A30" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="F30" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="H30" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="I30" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="J30" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="K30" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="L30" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="M30" s="2" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="31" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A31" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="E31" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="F31" t="s">
+        <v>151</v>
+      </c>
+      <c r="G31" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="H31" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="I31" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="J31" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="K31" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="L31" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="M31" s="2" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="32" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N32" s="2" t="s">
+        <v>142</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FD77BA2C-7AA3-418F-8351-D72AEC8E77F3}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData/>
@@ -1961,7 +3324,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{280D7C4D-D7D1-4AFC-BD87-8EB6A653F8BA}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData/>
@@ -1970,7 +3333,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{67637EB2-D239-45B9-A730-42F93D22D8D4}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData/>
@@ -1979,7 +3342,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A0A8D587-BB86-41E9-A0F7-5A4EF51A9768}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData/>
@@ -1988,7 +3351,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AED6AF45-3245-442D-AE41-351A488D42C4}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData/>
@@ -1997,7 +3360,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{602F758C-8C3E-4ED7-901C-A8CC7680A300}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData/>
@@ -2006,243 +3369,10 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CF830398-411F-494C-B50E-976F18D5C435}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100FB8DFF5778560F4887C4C7AA90F18950" ma:contentTypeVersion="9" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="52722438e1b4488aa8a60161ace39567">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="a48e72b4-5688-4929-9f7c-dafa23cdc8ca" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="d5371d62a652d9cc0189b9c8c7858a88" ns3:_="">
-    <xsd:import namespace="a48e72b4-5688-4929-9f7c-dafa23cdc8ca"/>
-    <xsd:element name="properties">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element name="documentManagement">
-            <xsd:complexType>
-              <xsd:all>
-                <xsd:element ref="ns3:MediaServiceDateTaken" minOccurs="0"/>
-                <xsd:element ref="ns3:MediaServiceMetadata" minOccurs="0"/>
-                <xsd:element ref="ns3:MediaServiceFastMetadata" minOccurs="0"/>
-                <xsd:element ref="ns3:MediaServiceSearchProperties" minOccurs="0"/>
-                <xsd:element ref="ns3:_activity" minOccurs="0"/>
-                <xsd:element ref="ns3:MediaServiceSystemTags" minOccurs="0"/>
-                <xsd:element ref="ns3:MediaServiceGenerationTime" minOccurs="0"/>
-                <xsd:element ref="ns3:MediaServiceEventHashCode" minOccurs="0"/>
-                <xsd:element ref="ns3:MediaLengthInSeconds" minOccurs="0"/>
-              </xsd:all>
-            </xsd:complexType>
-          </xsd:element>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="a48e72b4-5688-4929-9f7c-dafa23cdc8ca" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="MediaServiceDateTaken" ma:index="8" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceFastMetadata" ma:index="10" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceSearchProperties" ma:index="11" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="_activity" ma:index="12" nillable="true" ma:displayName="_activity" ma:hidden="true" ma:internalName="_activity">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceSystemTags" ma:index="13" nillable="true" ma:displayName="MediaServiceSystemTags" ma:hidden="true" ma:internalName="MediaServiceSystemTags" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceGenerationTime" ma:index="14" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceEventHashCode" ma:index="15" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaLengthInSeconds" ma:index="16" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Unknown"/>
-      </xsd:simpleType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
-    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
-    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
-    <xsd:element name="coreProperties" type="CT_coreProperties"/>
-    <xsd:complexType name="CT_coreProperties">
-      <xsd:all>
-        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
-        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
-        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
-          <xsd:annotation>
-            <xsd:documentation>
-                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
-                    </xsd:documentation>
-          </xsd:annotation>
-        </xsd:element>
-        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-      </xsd:all>
-    </xsd:complexType>
-  </xsd:schema>
-  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
-    <xs:element name="Person">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:DisplayName" minOccurs="0"/>
-          <xs:element ref="pc:AccountId" minOccurs="0"/>
-          <xs:element ref="pc:AccountType" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="DisplayName" type="xs:string"/>
-    <xs:element name="AccountId" type="xs:string"/>
-    <xs:element name="AccountType" type="xs:string"/>
-    <xs:element name="BDCAssociatedEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-        <xs:attribute ref="pc:EntityNamespace"/>
-        <xs:attribute ref="pc:EntityName"/>
-        <xs:attribute ref="pc:SystemInstanceName"/>
-        <xs:attribute ref="pc:AssociationName"/>
-      </xs:complexType>
-    </xs:element>
-    <xs:attribute name="EntityNamespace" type="xs:string"/>
-    <xs:attribute name="EntityName" type="xs:string"/>
-    <xs:attribute name="SystemInstanceName" type="xs:string"/>
-    <xs:attribute name="AssociationName" type="xs:string"/>
-    <xs:element name="BDCEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
-          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
-          <xs:element ref="pc:EntityId1" minOccurs="0"/>
-          <xs:element ref="pc:EntityId2" minOccurs="0"/>
-          <xs:element ref="pc:EntityId3" minOccurs="0"/>
-          <xs:element ref="pc:EntityId4" minOccurs="0"/>
-          <xs:element ref="pc:EntityId5" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="EntityDisplayName" type="xs:string"/>
-    <xs:element name="EntityInstanceReference" type="xs:string"/>
-    <xs:element name="EntityId1" type="xs:string"/>
-    <xs:element name="EntityId2" type="xs:string"/>
-    <xs:element name="EntityId3" type="xs:string"/>
-    <xs:element name="EntityId4" type="xs:string"/>
-    <xs:element name="EntityId5" type="xs:string"/>
-    <xs:element name="Terms">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermInfo">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermName" minOccurs="0"/>
-          <xs:element ref="pc:TermId" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermName" type="xs:string"/>
-    <xs:element name="TermId" type="xs:string"/>
-  </xs:schema>
-</ct:contentTypeSchema>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="a48e72b4-5688-4929-9f7c-dafa23cdc8ca" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B163AAC0-3015-4CB7-80F0-546613E40708}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DB7B87E3-F65A-4566-8036-DCFA61E2D7E3}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="a48e72b4-5688-4929-9f7c-dafa23cdc8ca"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{68A5F938-1F90-4C9B-A197-5D75696EB972}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="a48e72b4-5688-4929-9f7c-dafa23cdc8ca"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>